--- a/eval/error_analysis/representative_failures.xlsx
+++ b/eval/error_analysis/representative_failures.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,33 +456,33 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Paper found</t>
+          <t>Missing tokens</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>All tokens in paper</t>
+          <t>Model answers (dedup)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Missing tokens</t>
+          <t>Paper path</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Model answers (dedup)</t>
+          <t>Right model</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Paper path</t>
+          <t>Right answer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28559249</v>
+        <v>35945163</v>
       </c>
       <c r="B2" t="n">
         <v>5</v>
@@ -499,110 +499,98 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0 | Not reported</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/28559249/28559249.checked.md</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0 | 35</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35945163/35945163.checked.md</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35913500</v>
+        <v>36659824</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>No | Not applicable | Not reported</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0 | 112 | 118</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36659824/36659824.checked.md</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35913500</v>
+        <v>36660819</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>No | Not applicable | Not reported</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
-        </is>
-      </c>
+          <t>8 and 10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0 | 1045</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36660819/36660819.checked.md</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35945163</v>
+        <v>37993493</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -619,30 +607,26 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0 | 35 | Not reported | Not applicable</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/35945163/35945163.checked.md</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>600 | 0 | 598 | 31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37993493/37993493.checked.md</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>36659824</v>
+        <v>38090027</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -659,30 +643,26 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0 | 112 | **112** | 118</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/36659824/36659824.checked.md</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0 | 1040 | No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/38090027/38090027.checked.md</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36660819</v>
+        <v>40391923</v>
       </c>
       <c r="B7" t="n">
         <v>5</v>
@@ -699,121 +679,101 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8 and 10</t>
-        </is>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0 | 1045 | Not reported</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/36660819/36660819.checked.md</t>
-        </is>
-      </c>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>488 individuals had samples obtained for HIV sequencing. | Samples were obtained from 488 individuals for HIV sequencing. | 234 | 488</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40391923/40391923.checked.md</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36694270</v>
+        <v>40974886</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
-        </is>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Samples were obtained from 241 individuals. | 241 individuals had samples obtained for HIV sequencing. | 241</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>EVG, ABC, DTG</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3TC; TDF | No | Not reported | 3TC, TDF, EFV, LPV/r | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV) | NRTI, NNRTI, PI | 3TC, TDF, EFV</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/36694270/36694270.checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/40974886/40974886.checked.md</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36961945</v>
+        <v>41130593</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>The total number was not explicitly stated in the text provided. | Samples were obtained from a total of 54 individuals in the PURPOSE 1 and PURPOSE 2 trials. | 55 | 8603 | 60 | 66 | Not reported. | 53 | 55 (PURPOSE 1) and 11 (PURPOSE 2)</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>No | Not reported</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/36961945/36961945.checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/41130593/41130593.checked.md</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37376649</v>
+        <v>37775947</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -822,42 +782,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Plasma; PBMC</t>
-        </is>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>asia</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>South America, Africa, USA | No | Not reported | Africa, USA, South America</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PBMC</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Whole Blood | Whole blood | PBMC | No | Not reported</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/37376649/37376649.checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/37775947/37775947.checked.md</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>37554471</v>
+        <v>41140464</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -866,163 +822,143 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>No | Not reported</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/37554471/37554471.checked.md</t>
-        </is>
-      </c>
+          <t>Not available (deposited 2015-2025)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The sequenced samples were obtained between 2015 and 2025. | The sequenced samples were obtained from the years 2015 to 2025. | 2015–2025 | 2015-2025</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41140464/41140464.checked.md</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37701387</v>
+        <v>37957382</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RT, IN</t>
-        </is>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>No | Not reported | "Not reported"</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/37701387/37701387.checked.md</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No | Not reported. | Not reported</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37957382/37957382.checked.md</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37775947</v>
+        <v>41091504</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
-        </is>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
+          <t>Yes (site-directed mutants)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>The paper does not mention whether samples were cloned prior to sequencing. | Not reported | No</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>South America, Africa, USA | No | Not reported | Africa, USA, South America | Multiple</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/37775947/37775947.checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/41091504/41091504.checked.md</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37823653</v>
+        <v>41130593</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
-        </is>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
+          <t>Yes (single genome)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>The text does not indicate that samples were cloned prior to sequencing. | No, samples were not cloned prior to sequencing. | No | No. | Not reported</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NFLG</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Near full length genome | Env | Envelope | "Env". | No</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/37823653/37823653.checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/41130593/41130593.checked.md</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>38058846</v>
+        <v>35913500</v>
       </c>
       <c r="B15" t="n">
         <v>9</v>
@@ -1039,73 +975,65 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
-        </is>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>No | IN | Not reported</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/38058846/38058846.checked.md</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No | Not applicable | Not reported</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>38090027</v>
+        <v>35945163</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0 | Not reported | **1040** | 1040 | No</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers/38090027/38090027.checked.md</t>
-        </is>
-      </c>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No | Not reported</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35945163/35945163.checked.md</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>40431710</v>
+        <v>37541705</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1114,42 +1042,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No | Not reported</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Next-generation sequencing (NGS) was employed. | Next generation sequencing was used for genotypic resistance tests. | NGS | Not reported | Illumina sequencing | Unknown</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/40431710/40431710_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/37541705/37541705.checked.md</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>40431710</v>
+        <v>37554471</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1158,38 +1078,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
-        </is>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>The drugs included zidovudine, didanosine, tenofovir, darunavir, and others. | Zidovudine (AZT), ritonavir (RTV), didanosine (ddI), abacavir (ABC), tenofovir disoproxil (TDF), lopinavir (LPV), etravirine (ETR), atazanavir (ATV), raltegravir (RAL), emtricitabine (FTC), dolutegravir (DTG), darunavir (DRV), and bictegravir (BIC). | Zidovudine (AZT), Lamivudine (3TC), Abacavir (ABC), Tenofovir (TDF), Emtricitabine (FTC), Delavirdine (DLV), Efavirenz (EFV), Rilpivirine (RPV), Doravirine (DOR), Indinavir (IDV), Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV), Raltegravir (RAL), Dolutegravir (DTG), Bictegravir (BIC), Fostemsavir (FTR) | AZT, 3TC, ddI, ABC, TDF, RTV, DRV, ETR, DTG, BIC, DOR | AZT, 3TC, TDF, DOR, RPV, DRV, ATV, BIC, RAL | Not reported | Zidovudine, Didanosine, Abacavir, Tenofovir, Lopinavir, Atazanavir, Darunavir, Raltegravir, Dolutegravir, Elvitegravir, Bictegravir, Rilpivirine, Doravirine | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207) | AZT, RTV, IDV, 3TC, DLV, ABC, NFV, EFV, TDF, LPV/r, ETR, ATV/r, PBO/RAL, DRV/r, RAL, DRV/c, DTG, FTC, EVG, BIC, RPV, DOR, FTR | AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DTG, DRV, BIC</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/40431710/40431710_checked.md</t>
-        </is>
-      </c>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No | Not reported</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37554471/37554471.checked.md</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40779404</v>
+        <v>37823653</v>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1198,42 +1114,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
-        </is>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
+          <t>NFLG, Envelope</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nflg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Near full length genome | Env | Envelope | No</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TFV (no other ARVs specified, Data in supplementary methods)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Individuals received Tenofovir (TFV) and various classes including integrase inhibitors (INSTIs), non-nucleoside RT inhibitors (NNRTIs), and protease inhibitors (PIs). | Participants received Tenofovir, INSTIs, NNRTIs, and PIs before sample sequencing. | TDF/TAF, EFV, ETR, RPV, NVP, DTG, BIC, LPV/r, ATV | Not reported | Tenofovir (TFV), Raltegravir, Elvitegravir, Dolutagravir, Bictegravir, Nevirapine, Delavirdine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir | Tenofovir (TFV), INSTIs, NNRTIs, PIs | TFV, INSTIs, NNRTIs, and PIs. | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN) | Bictegravir, Emtricitabine, Tenofovir Alafenamide | TFV, INSTIs, NNRTIs, PIs</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/40779404/40779404_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/37823653/37823653.checked.md</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40872801</v>
+        <v>37938856</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1242,42 +1154,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No | RT | Not reported</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sanger</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>The method for sequencing is not specified, but studies referenced typically utilize Sanger sequencing or next-generation sequencing. | The paper does not specify the exact sequencing method used. | Not reported | Unknown | **Not reported** | Unknown. | Not applicable</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/40872801/40872801_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/37938856/37938856.checked.md</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>41012586</v>
+        <v>38058846</v>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1286,39 +1190,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
-        </is>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No | IN | Not reported</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Plasma (presumably)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>The paper does not specify the type of samples that were sequenced. | The paper does not specify the type of samples sequenced. | Not reported | Unknown | Unknown. | Plasma</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/41012586/41012586_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/38058846/38058846.checked.md</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>41057785</v>
+        <v>40431710</v>
       </c>
       <c r="B22" t="n">
         <v>10</v>
@@ -1335,160 +1231,2852 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
-        </is>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Next-generation sequencing (NGS) was employed. | Next generation sequencing was used for genotypic resistance tests. | Not reported | Illumina sequencing | NGS | Unknown</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sanger (not stated)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>The paper does not specify the exact method used for sequencing. | The paper does not specify the method used for sequencing. | Not reported | Unknown | "Not reported"</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/41057785/41057785_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/40431710/40431710.checked.md</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>41091504</v>
+        <v>40872801</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>The method for sequencing is not specified, but studies referenced typically utilize Sanger sequencing or next-generation sequencing. | The paper does not specify the exact sequencing method used. | Not reported | Unknown | Unknown.</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Yes (site-directed mutants)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>The paper does not mention whether samples were cloned prior to sequencing. | Not reported | No</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/41091504/41091504_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/40872801/40872801.checked.md</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>41130593</v>
+        <v>40974886</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
+          <t>NGS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>GenoSure Archive sequencing was used for genotyping. | The GenoSure Archive method was used for sequencing. | Not reported | Unknown | Not reported (but likely Sanger sequencing or NGS). | Unknown.</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>The total number was not explicitly stated in the text provided. | Samples were obtained from a total of 54 individuals in the PURPOSE 1 and PURPOSE 2 trials. | 52 | 55 | 8603 | 60 | 77 | 66 | Not reported. | 53 | 55 (PURPOSE 1) and 11 (PURPOSE 2)</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/41130593/41130593_checked.md</t>
-        </is>
-      </c>
+          <t>advanced-prompting/papers/40974886/40974886.checked.md</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>41130593</v>
+        <v>41057785</v>
       </c>
       <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sanger (not stated)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>The paper does not specify the exact method used for sequencing. | The paper does not specify the method used for sequencing. | Not reported | Unknown</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41057785/41057785.checked.md</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>37279764</v>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Whole Blood | Plasma | Blood | Blood samples | Plasma or whole blood</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37279764/37279764.checked.md</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>40400229</v>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Clinical samples from patients diagnosed with HIV during the trial were sequenced. | The paper does not specify the type of clinical specimens sequenced, whether blood or other fluids. | Not reported | Unknown | Not reported.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40400229/40400229.checked.md</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>40965168</v>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Clinical plasma samples from patients were sequenced. | The paper sequenced viral supernatants obtained from patient isolates. | Plasma | Plasma.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40965168/40965168.checked.md</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>41012586</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Plasma (presumably)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>The paper does not specify the type of samples that were sequenced. | The paper does not specify the type of samples sequenced. | Not reported | Unknown | Unknown. | Plasma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41012586/41012586.checked.md</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>40400229</v>
+      </c>
+      <c r="B30" t="n">
+        <v>13</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Were the patients in the study in a clinical trial?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes, the patients were part of the PrEP Impact trial. | Yes | Yes.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40400229/40400229.checked.md</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>37755428</v>
+      </c>
+      <c r="B31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>INSTI | NRTI, INSTI | NRTI, INSTIs | NRTIs, INSTIs</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37755428/37755428.checked.md</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>36694270</v>
+      </c>
+      <c r="B32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3TC, TDF, EFV, LPV/r, EVG, ABC, DTG</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>evg, abc, dtg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3TC; TDF | No | Not reported | 3TC, TDF, EFV, LPV/r | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV) | NRTI, NNRTI, PI | 3TC, TDF, EFV</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36694270/36694270.checked.md</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>37541705</v>
+      </c>
+      <c r="B33" t="n">
+        <v>16</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>lpv, dtg, abc, 3tc</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopinavir/ritonavir, Dolutegravir, Raltegravir | Lopinavir (LPV), Dolutegravir (DTG), Raltegravir (RAL) | Dolutegravir, Abacavir, Lamivudine | No | NRTI (Abacavir, Lamivudine), NNRTI (Nevirapine, Efavirenz), PI (Lopinavir), INSTI (Raltegravir)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37541705/37541705.checked.md</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>37946329</v>
+      </c>
+      <c r="B34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3TC, NVP, ETR, ABC, DTG | NVP, ETR, ABC, 3TC, DTG, ATV, LPV, RAL, SQV | 3TC, NVP | Abacavir (ABC), Nevirapine (NVP), Efavirenz (EFV), Raltegravir (RAL) | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN) | 3TC, DTG, RAL | NVP, ETR, ABC, DTG, BIC, CAB, RAL, EVG, LPV, ATV, APV, DOR, RPV, DLV, AZT, D4T, FTC, TFV | NRTI, NNRTI, PI, INSTI | NRTIs, NNRTIs, PIs, INSTIs</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37946329/37946329.checked.md</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>40431710</v>
+      </c>
+      <c r="B35" t="n">
+        <v>16</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>The drugs included zidovudine, didanosine, tenofovir, darunavir, and others. | Zidovudine (AZT), ritonavir (RTV), didanosine (ddI), abacavir (ABC), tenofovir disoproxil (TDF), lopinavir (LPV), etravirine (ETR), atazanavir (ATV), raltegravir (RAL), emtricitabine (FTC), dolutegravir (DTG), darunavir (DRV), and bictegravir (BIC). | AZT, 3TC, ddI, ABC, TDF, RTV, DRV, ETR, DTG, BIC, DOR | AZT, 3TC, TDF, DOR, RPV, DRV, ATV, BIC, RAL | Zidovudine, Didanosine, Abacavir, Tenofovir, Lopinavir, Atazanavir, Darunavir, Raltegravir, Dolutegravir, Elvitegravir, Bictegravir, Rilpivirine, Doravirine | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207) | AZT, RTV, IDV, 3TC, DLV, ABC, NFV, EFV, TDF, LPV/r, ETR, ATV/r, PBO/RAL, DRV/r, RAL, DRV/c, DTG, FTC, EVG, BIC, RPV, DOR, FTR | AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DTG, DRV, BIC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40431710/40431710.checked.md</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>40596906</v>
+      </c>
+      <c r="B36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>The drugs included zidovudine (ZDV), lamivudine (3TC), and nevirapine (NVP). | Individuals in the study received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV) before sample sequencing. | Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV) | Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV) | ZDV, 3TC, NVP, LPV, EFV | ZDV, 3TC, NVP, lopinavir/ritonavir, EFV | Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV). | Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Lopinavir/Ritonavir | ZDV, 3TC, EFV, NVP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40596906/40596906.checked.md</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>40779404</v>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Individuals received Tenofovir (TFV) and various classes including integrase inhibitors (INSTIs), non-nucleoside RT inhibitors (NNRTIs), and protease inhibitors (PIs). | Participants received Tenofovir, INSTIs, NNRTIs, and PIs before sample sequencing. | Not reported | Tenofovir (TFV), Raltegravir, Elvitegravir, Dolutagravir, Bictegravir, Nevirapine, Delavirdine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir | Tenofovir (TFV), INSTIs, NNRTIs, PIs | TFV, INSTIs, NNRTIs, and PIs. | Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN) | TFV, INSTIs, NNRTIs, PIs</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40779404/40779404.checked.md</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37701387</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No | Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37701387/37701387.checked.md</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>40965168</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from patient samples?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from 24 patient samples. | Yes, the paper reports HIV-1 sequences from patient plasma samples. | Yes | Yes.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40965168/40965168.checked.md</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>23749954</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes | We recently reported the preferential selection of the K65R resistance</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/23749954/23749954.checked.md</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>We recently reported the preferential selection of the K65R resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>38005921</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes | No</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/38005921/38005921.checked.md</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>35913500</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0 | 51</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40857111</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>7 (Uncertain)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>208 participants had samples obtained. | The paper mentions resistance testing data for 22 participants. | 208 | Unknown | 330 | 7 (DTG+F/TDF group) and 6 (B/F/TAF group)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40857111/40857111.checked.md</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7 (DTG+F/TDF group) and 6 (B/F/TAF group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>40965168</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>A total of 24 individuals had samples obtained for sequencing. | The paper involved 24 patient samples for HIV sequencing. | 24</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40965168/40965168.checked.md</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>41056006</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>183 participants were enrolled. | 182 participants received at least one dose of study drug, and those who met virologic failure criteria were included in the resistance analysis population. | Not reported | 182 | 10 | 183</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41056006/41056006.checked.md</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>37104815</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No | France | Sub-Saharan Africa | Not reported</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37104815/37104815.checked.md</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>37701387</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No | Italy | Not applicable | Not reported</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37701387/37701387.checked.md</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>38090027</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No | Not reported | Italy</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/38090027/38090027.checked.md</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>41012586</v>
+      </c>
+      <c r="B49" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>The paper does not disclose specific countries from which the sequenced samples were obtained. | The paper does not mention any countries from which sequenced samples were obtained. | Italy | Not Found | Not reported | Not Found.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41012586/41012586.checked.md</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>35913500</v>
+      </c>
+      <c r="B50" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2021-2022</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No | Not applicable | 2021-2022</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2021-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>37701387</v>
+      </c>
+      <c r="B51" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2020-2021</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>No | 2020–2021 | Not applicable | Not reported</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37701387/37701387.checked.md</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2020–2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>41088231</v>
+      </c>
+      <c r="B52" t="n">
         <v>8</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Yes (single genome)</t>
-        </is>
-      </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Yes (single genome)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>The text does not indicate that samples were cloned prior to sequencing. | No, samples were not cloned prior to sequencing. | Not reported | No | No.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>advanced-prompting/papers_2025_30/41130593/41130593_checked.md</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes, samples were cloned prior to sequencing. | No, samples were not cloned prior to sequencing. | No | No.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41088231/41088231.checked.md</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>GPT-4o base</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Yes, samples were cloned prior to sequencing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>21115794</v>
+      </c>
+      <c r="B53" t="n">
+        <v>9</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No | Not reported | IN</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/21115794/21115794.checked.md</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>36659824</v>
+      </c>
+      <c r="B54" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No | Not reported | PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36659824/36659824.checked.md</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>36660819</v>
+      </c>
+      <c r="B55" t="n">
+        <v>9</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No | PR, RT, IN | Not reported</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36660819/36660819.checked.md</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>36706364</v>
+      </c>
+      <c r="B56" t="n">
+        <v>9</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>No | Not reported | PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36706364/36706364.checked.md</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>37340869</v>
+      </c>
+      <c r="B57" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No | Not reported | RT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37340869/37340869.checked.md</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>38005921</v>
+      </c>
+      <c r="B58" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT; Protease, PR | PR, RT | Protease, Reverse transcriptase | No | PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/38005921/38005921.checked.md</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>38090027</v>
+      </c>
+      <c r="B59" t="n">
+        <v>9</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RT, IN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No | Not reported | Pol, RT, IN</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/38090027/38090027.checked.md</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Pol, RT, IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>41012586</v>
+      </c>
+      <c r="B60" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>The paper does not specify which HIV genes were sequenced. | The paper does not report sequencing of specific HIV genes. | Not reported | Unknown | Not reported. | PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41012586/41012586.checked.md</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>41088231</v>
+      </c>
+      <c r="B61" t="n">
+        <v>9</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>The vif and env gene regions were reported to have been sequenced. | The sequenced genes include the near full-length genome (NFLG), specifically mentioning regions of vif and env genes, and the pol gene. | Pol, Env | Near full length genome | Full genome. | PR, RT, IN, Pol, CA, Env</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41088231/41088231.checked.md</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B base</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Full genome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>36454248</v>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sanger sequencing | No</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36454248/36454248.checked.md</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>37071019</v>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>No | Sanger sequencing | Not reported</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37071019/37071019.checked.md</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>41056006</v>
+      </c>
+      <c r="B64" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>What method was used for sequencing?</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Sanger</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>GenoSure Gag-Pro and PhenoSense Gag-Pro assays. | The paper does not specify the exact sequencing method used. | Not reported | Unknown | Unknown. | Sanger sequencing | Not reported (the paper does not mention the sequencing method)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41056006/41056006.checked.md</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sanger sequencing</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>35945163</v>
+      </c>
+      <c r="B65" t="n">
+        <v>11</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>No | Not applicable | Plasma, serum, or other bodily fluids</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35945163/35945163.checked.md</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Plasma, serum, or other bodily fluids</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>37104815</v>
+      </c>
+      <c r="B66" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Whole Blood, Semen</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Whole Blood, Other | Plasma; PBMC | Plasma | Plasma; Semen | Plasma; PBMC; Semen | Plasma, Semen</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37104815/37104815.checked.md</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>GPT-4o base</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Whole Blood, Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>37376649</v>
+      </c>
+      <c r="B67" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>pbmc</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Whole Blood | PBMC | No</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37376649/37376649.checked.md</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>40596906</v>
+      </c>
+      <c r="B68" t="n">
+        <v>11</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Samples sequenced were from HIV-1 infected individuals, specifically from mother-child pairs. | The sequenced samples were clinical specimens from mother-child pairs with confirmed vertical transmission of HIV-1. | Not reported | Unknown | Plasma | Not reported.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40596906/40596906.checked.md</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>40779404</v>
+      </c>
+      <c r="B69" t="n">
+        <v>11</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>The sequenced samples were proviral DNA from whole blood. | The paper mentions that whole blood samples were used for sequencing. | Not reported | Whole Blood | Whole Blood.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40779404/40779404.checked.md</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>GPT-4o base</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>The sequenced samples were proviral DNA from whole blood.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>40857111</v>
+      </c>
+      <c r="B70" t="n">
+        <v>11</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>HIV-1 patient samples. | The paper does not specify the type of samples that were sequenced. | Not reported | Unknown | Plasma | Unknown.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40857111/40857111.checked.md</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>40974886</v>
+      </c>
+      <c r="B71" t="n">
+        <v>11</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PBMC (Whole blood OK)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>The sequenced samples included whole blood samples from participants. | Whole blood and proviral DNA samples were sequenced. | Whole blood | Whole blood.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40974886/40974886.checked.md</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Whole blood and proviral DNA samples were sequenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>41057785</v>
+      </c>
+      <c r="B72" t="n">
+        <v>11</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Plasma (not stated)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>The samples sequenced were from individuals living with HIV-1. | The paper does not specify the type of clinical specimens sequenced. | Not reported | Unknown | Plasma</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41057785/41057785.checked.md</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>35913500</v>
+      </c>
+      <c r="B73" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>No | Not applicable | Yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>40974886</v>
+      </c>
+      <c r="B74" t="n">
+        <v>12</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>No, the study excluded participants with prior virological failure on INSTI regimens. | No, the study included individuals without prior virological failure. | Not reported | No | Yes. | No.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/40974886/40974886.checked.md</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>35913500</v>
+      </c>
+      <c r="B75" t="n">
+        <v>14</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>No | Yes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35913500/35913500.checked.md</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>36659824</v>
+      </c>
+      <c r="B76" t="n">
+        <v>14</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>No | Yes</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36659824/36659824.checked.md</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>36659824</v>
+      </c>
+      <c r="B77" t="n">
+        <v>15</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>No | NRTIs, INSTIs</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36659824/36659824.checked.md</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>NRTIs, INSTIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>36931676</v>
+      </c>
+      <c r="B78" t="n">
+        <v>15</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>nnrti, insti</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No | NRTI, INSTI, PI | Not reported | **Not reported**</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36931676/36931676.checked.md</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>NRTI, INSTI, PI</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>35730213</v>
+      </c>
+      <c r="B79" t="n">
+        <v>16</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EFV, DTG, TDF, 3TC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Efavirenz (EFV), Dolutegravir (DTG) | No | Tenofovir disoproxil fumarate (TDF), lamivudine (3TC), efavirenz (EFV) | EFV, DTG | EFV</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/35730213/35730213.checked.md</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Tenofovir disoproxil fumarate (TDF), lamivudine (3TC), efavirenz (EFV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>36454248</v>
+      </c>
+      <c r="B80" t="n">
+        <v>16</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>3TC, TDF, AZT, D4T, ABC, DDI, FTC, EFV, LPV, DRV, NFV, RAL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>azt</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lamivudine, Zidovudine, Lopinavir/Ritonavir, Efavirenz | Lamivudine (3TC), Zidovudine (AZT), Lopinavir (LPV), Ritonavir (RTV), Efavirenz (EFV), Darunavir (DRV), Raltegravir (RAL), Emtricitabine (FTC), Tenofovir (TFV), Dolutegravir (DTG), Abacavir (ABC), Etravirine (ETR), Rilpivirine (RPV), Nevirapine (NVP), Nelfinavir (NFV), Stavudine (D4T), Didanosine (DDI), Lamivudine (3TC), Zidovudine (ZDV), Doravirine (DOR), Bictegravir (BIC), Cabotegravir (CAB), Elvitegravir (EVG), Raltegravir (RAL) | Lamivudine, zidovudine, lopinavir/r, efavirenz | Lamivudine, Zidovudine, Lopinavir, Ritonavir, Raltegravir | Lamivudine, Zidovudine, Lopinavir/ritonavir, Efavirenz, Raltegravir | Not reported | Lamivudine, Zidovudine, Lopinavir/Ritonavir, and Efavirenz | No | NRTIs (zidovudine, lamivudine, tenofovir, emtricitabine), NNRTIs (efavirenz, nevirapine), PIs (lopinavir/ritonavir, atazanavir, darunavir), and INSTIs (raltegravir)</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36454248/36454248.checked.md</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Lamivudine (3TC), Zidovudine (AZT), Lopinavir (LPV), Ritonavir (RTV), Efavirenz (EFV), Darunavir (DRV), Raltegravir (RAL), Emtricitabine (FTC), Tenofovir (TFV), Dolutegravir (DTG), Abacavir (ABC), Etravirine (ETR), Rilpivirine (RPV), Nevirapine (NVP), Nelfinavir (NFV), Stavudine (D4T), Didanosine (DDI), Lamivudine (3TC), Zidovudine (ZDV), Doravirine (DOR), Bictegravir (BIC), Cabotegravir (CAB), Elvitegravir (EVG), Raltegravir (RAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>36597160</v>
+      </c>
+      <c r="B81" t="n">
+        <v>16</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TDF,FTC,EVG</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>evg</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tenofovir disoproxil fumarate, Emtricitabine, Ritonavir-boosted Protease Inhibitors, NNRTIs, Integrase Inhibitors | No | Not reported | Elvitegravir, cobicistat, emtricitabine, tenofovir disoproxil fumarate | Ritonavir-boosted PIs, NNRTIs, INSTIs | Elvitegravir (EVG), Raltegravir (RAL), Dolutegravir (DTG), Bictegravir (BIC), cabotegravir (CAB), Lenacapavir (LEN) | TDF, FTC, PI/r</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36597160/36597160.checked.md</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Elvitegravir, cobicistat, emtricitabine, tenofovir disoproxil fumarate</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>36659824</v>
+      </c>
+      <c r="B82" t="n">
+        <v>16</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>BIC, FTC, TAF</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No | FTC, BIC</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36659824/36659824.checked.md</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>FTC, BIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>36931676</v>
+      </c>
+      <c r="B83" t="n">
+        <v>16</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>dtg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>No | Dolutegravir | Not reported | **Not reported**</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/36931676/36931676.checked.md</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Dolutegravir</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>37340869</v>
+      </c>
+      <c r="B84" t="n">
+        <v>16</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CAB, RPV</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Rilpivirine (RPV) | No | Not reported | Cabotegravir, Rilpivirine</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37340869/37340869.checked.md</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Cabotegravir, Rilpivirine</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>37495103</v>
+      </c>
+      <c r="B85" t="n">
+        <v>16</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>TDF, FTC, EFV, ABC, 3TC, DTG, LPV, Elsulfavirine, RAL, DRV, AZT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ftc</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tenofovir (TDF), Lamivudine (3TC), Efavirenz (EFV), Abacavir (ABC) | Tenofovir (TDF), Lamivudine (3TC), Efavirenz (EFV), Abacavir (ABC), Dolutegravir (DTG), Lopinavir (LPV), Raltegravir (RAL), Darunavir (DRV), Elsulfavirine (ESV) | Tenofovir (TDF), Lamivudine (3TC), Efavirenz (EFV), Abacavir (ABC), Dolutegravir (DTG) | Abacavir (ABC), Zidovudine (AZT), Lamivudine (3TC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Lopinavir (LPV), Dolutegravir (DTG) | TDF, 3TC, EFV, ABC, DTG, LPV/r, ETR | TDF, 3TC, EFV | Tenofovir (TDF), Lamivudine (3TC), Efavirenz (EFV), Abacavir (ABC), Ritonavir-boosted Lopinavir (LPV/r), Dolutegravir (DTG) | ABC, 3TC, TDF, EFV, LPV/r, DTG, RAL, DOR, ETR, RPV | TDF, 3TC, ABC, EFV, DTG, LPV/r</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37495103/37495103.checked.md</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Tenofovir (TDF), Lamivudine (3TC), Efavirenz (EFV), Abacavir (ABC), Dolutegravir (DTG), Lopinavir (LPV), Raltegravir (RAL), Darunavir (DRV), Elsulfavirine (ESV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>37632026</v>
+      </c>
+      <c r="B86" t="n">
+        <v>16</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AZT, D4T, XTC, TDF, ATV, LPV, DRV</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>No | NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine (AZT), Lamivudine (3TC), Emtricitabine (FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Efavirenz (EFV); PI (Protease Inhibitor), including Lopinavir (LPV), Atazanavir (ATV), Darunavir (DRV) | Zidovudine (AZT), Tenofovir (TDF), Abacavir (ABC), Lamivudine/Emtricitabine (3TC/FTC) | TDF, AZT, ABC, EFV, ATV, LPV, DRV | AZT, 3TC, TDF, EFV, NVP, LPV/r, ATV/r | Not reported | Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG), Bictegravir (BIC), cabotegravir (CAB), Lenacapavir (LEN) | AZT, TDF, ABC, EFV, NVP, ATV/r, LPV/r, DRV/r</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37632026/37632026.checked.md</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>TDF, AZT, ABC, EFV, ATV, LPV, DRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>37755428</v>
+      </c>
+      <c r="B87" t="n">
+        <v>16</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Dolutegravir | Tenofovir (TFV), Lamivudine (3TC), Dolutegravir (DTG) | Tenofovir, Lamivudine, Dolutegravir, Zidovudine | DTG, tenofovir, and lamivudine | DTG</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/37755428/37755428.checked.md</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>41057785</v>
+      </c>
+      <c r="B88" t="n">
+        <v>16</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>The study participants received drugs like AZT, TDF, and other NRTIs and PIs. | Specific drugs received included AZT, TDF, D4T, and TDF. | AZT, TDF, Efavirenz | AZT, TDF | AZT, D4T, TDF, ABC | AZT, TDF, NNRTIs | The drugs that were received by individuals in the study before sample sequencing are Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN). | Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV) | Not reported</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>advanced-prompting/papers/41057785/41057785.checked.md</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B base</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>The drugs that were received by individuals in the study before sample sequencing are Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN).</t>
         </is>
       </c>
     </row>
